--- a/outputs/daily/predictions_2026-07-02.xlsx
+++ b/outputs/daily/predictions_2026-07-02.xlsx
@@ -924,31 +924,31 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2.156709913644509</v>
+        <v>2.205014679990379</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8525531518227769</v>
+        <v>0.8592483854769061</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7227486138084207</v>
+        <v>0.7222039965520262</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1818373051607281</v>
+        <v>0.188657170134955</v>
       </c>
       <c r="R2" t="n">
-        <v>0.09541408103085124</v>
+        <v>0.08913883331301876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5392625730764177</v>
+        <v>0.5631961434208144</v>
       </c>
       <c r="T2" t="n">
-        <v>2.127719598322003</v>
+        <v>2.215546446223586</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7122804016779973</v>
+        <v>0.7244535537764141</v>
       </c>
       <c r="V2" t="n">
         <v>0.6382174197326057</v>
@@ -966,25 +966,25 @@
         <v>0.534342685869051</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6635428598540385</v>
+        <v>0.6713091493158296</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2094366223327065</v>
+        <v>0.204690046198882</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.127020517813255</v>
+        <v>0.1240008044852882</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5788750607609623</v>
+        <v>0.591044016149917</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4211249392390377</v>
+        <v>0.408955983850083</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.516366815323138</v>
+        <v>0.5218037771291838</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.483633184676862</v>
+        <v>0.4781962228708162</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -992,22 +992,22 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>2.156755</v>
+        <v>2.20563</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.853305</v>
+        <v>0.85864</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.01006</v>
+        <v>3.06427</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6783612573932899</v>
+        <v>0.6800849828561799</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.19538076051701</v>
+        <v>0.1969220624732446</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1262579820897002</v>
+        <v>0.1229929546705755</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.6783612573932899</v>
+        <v>0.6800849828561799</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5202</v>
+        <v>0.5245</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4798</v>
+        <v>0.4755</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.5202</v>
+        <v>0.5245</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.7956</v>
+        <v>0.7982</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2044</v>
+        <v>0.2018</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.7956</v>
+        <v>0.7982</v>
       </c>
       <c r="BF2" t="n">
         <v>0.6</v>
@@ -1073,33 +1073,33 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>10.48063335302322</v>
+        <v>11.21845510910394</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.1262579820897002</v>
+        <v>0.1229929546705755</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.03084390105884897</v>
+        <v>0.03385412135755674</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.3232636181747208</v>
+        <v>0.3797909407079072</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>OVER_2_5</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>1.85438420896733</v>
+        <v>11.21845510910394</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.5788750607609623</v>
+        <v>0.1229929546705755</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.03961248768454462</v>
+        <v>0.03385412135755674</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.07345677164013242</v>
+        <v>0.3797909407079072</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.1147240083288672</v>
+        <v>0.1135034880030833</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.09752768881264667</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BV2" t="n">
-        <v>0.09977155082276307</v>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BX2" t="n">
-        <v>0.09780831489051821</v>
+        <v>0.09730588976793519</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0973178415658854</v>
+        <v>0.09410433414644777</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.08247546869863431</v>
+        <v>0.08342561909230352</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.07031472078708147</v>
+        <v>0.07168332851247315</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>0.05839897370112284</v>
+        <v>0.05553516854065325</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.0444689152437055</v>
+        <v>0.04598867869645373</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1171,15 +1171,15 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.04169339356719297</v>
+        <v>0.04190025457578039</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.03866388641645137</v>
+        <v>0.03951569792014406</v>
       </c>
     </row>
     <row r="3">
@@ -1238,31 +1238,31 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.791507907214497</v>
+        <v>1.841431554723644</v>
       </c>
       <c r="N3" t="n">
-        <v>1.014474706429132</v>
+        <v>1.025051058919985</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5448621465346269</v>
+        <v>0.5556445471127791</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.261470636194702</v>
+        <v>0.2570944539568842</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1936672172706711</v>
+        <v>0.1872609989303367</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5146100206945362</v>
+        <v>0.5399695517327212</v>
       </c>
       <c r="T3" t="n">
-        <v>1.786916468404082</v>
+        <v>1.87768673660253</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9430835315959181</v>
+        <v>0.9623132633974697</v>
       </c>
       <c r="V3" t="n">
         <v>0.5313399982729576</v>
@@ -1280,25 +1280,25 @@
         <v>0.5593849335454074</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5450354387098046</v>
+        <v>0.5541785503040936</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2535075059120115</v>
+        <v>0.2484434349893453</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2014570553781833</v>
+        <v>0.1973780147065615</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5319698002793742</v>
+        <v>0.5462399118917296</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4680301997206258</v>
+        <v>0.4537600881082704</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5421315501356812</v>
+        <v>0.5502699560704258</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4578684498643188</v>
+        <v>0.4497300439295742</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -1306,22 +1306,22 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>1.79179</v>
+        <v>1.841955</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.01593</v>
+        <v>1.02579</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.80772</v>
+        <v>2.867745</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5401727176868373</v>
+        <v>0.5467714558166702</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2528572606432851</v>
+        <v>0.2498407700174914</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.2069700216698777</v>
+        <v>0.2033877741658384</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.5401727176868373</v>
+        <v>0.5467714558166702</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.5458</v>
+        <v>0.5522</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4542</v>
+        <v>0.4478</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>0.5458</v>
+        <v>0.5522</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6919</v>
+        <v>0.6967</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.3081</v>
+        <v>0.3033</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.6919</v>
+        <v>0.6967</v>
       </c>
       <c r="BF3" t="n">
         <v>0.6</v>
@@ -1388,20 +1388,20 @@
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>OVER_2_5</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>1.943219058677412</v>
+        <v>5.340140262586187</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.5319698002793742</v>
+        <v>0.2033877741658384</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01735977958483814</v>
+        <v>0.01612677523550168</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.03373385454369648</v>
+        <v>0.08611924174078034</v>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>0.120845692681996</v>
+        <v>0.1181402450241515</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="BV3" t="n">
-        <v>0.0984072790875495</v>
+        <v>0.09888507957738887</v>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BX3" t="n">
+        <v>0.09646844292963926</v>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BX3" t="n">
-        <v>0.09730625042888297</v>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
       <c r="BZ3" t="n">
-        <v>0.09700318644112389</v>
+        <v>0.09403546360417835</v>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="CB3" t="n">
-        <v>0.07143349900552251</v>
+        <v>0.06763895268063407</v>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="CD3" t="n">
-        <v>0.05876580620426958</v>
+        <v>0.06069670194172082</v>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="CF3" t="n">
-        <v>0.05792732517809186</v>
+        <v>0.05921334494856492</v>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
@@ -1465,23 +1465,23 @@
         </is>
       </c>
       <c r="CH3" t="n">
-        <v>0.05572495391217861</v>
+        <v>0.05504535602866954</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.05068112776609473</v>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="CJ3" t="n">
-        <v>0.05033651508839776</v>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
       <c r="CL3" t="n">
-        <v>0.04991584778141571</v>
+        <v>0.04758428658886595</v>
       </c>
     </row>
     <row r="4">
